--- a/moduleproj2/temp_results/auto_result.xlsx
+++ b/moduleproj2/temp_results/auto_result.xlsx
@@ -471,7 +471,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-18 10:58:11</t>
+          <t>2026-05-19 02:02:20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -481,17 +481,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CWE-79</t>
+          <t>CWE-200</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>A03:2021-Injection</t>
+          <t>A05:2021-Security Misconfiguration</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>스크립트 삽입 취약점</t>
+          <t>보안 구성 오류</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -501,12 +501,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>HTML 소스코드에서 iframe 태그와 외부 스크립트를 사용하여 다른 도메인에서 콘텐츠를 로드하고 있습니다. 이는 악의적인 사용자가 스크립트를 삽입하여 사용자 정보를 탈취할 수 있는 위험을 내포하고 있습니다.</t>
+          <t>HTML 소스코드에서 'manager webapp'에 대한 접근이 제한되어 있다고 명시되어 있지만, 사용자 정의는 $CATALINA_HOME/conf/tomcat-users.xml 파일에서 이루어지며, 이 파일의 위치가 노출되어 있습니다. 이는 공격자가 관리자 접근을 시도할 수 있는 정보를 제공할 수 있습니다.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>iframe 태그를 사용하여 외부 콘텐츠를 로드하는 부분을 제거하거나, 신뢰할 수 있는 도메인에서만 콘텐츠를 로드하도록 제한해야 합니다. 또한, 입력값 검증을 통해 사용자 입력을 필터링하고, 출력값 인코딩을 적용하여 스크립트 삽입을 방지해야 합니다. 마지막으로, 하드코딩된 URL이나 API 키가 있다면 이를 환경 변수로 분리하여 관리하는 것이 중요합니다.</t>
+          <t>[수정 위치]: HTML 소스코드의 'Managing Tomcat' 섹션에서 사용자 정의 파일 경로를 제거하거나, 해당 정보를 비공식적으로 제공하는 방법으로 변경해야 합니다. 
+[코드 레벨 가이드]: Tomcat의 사용자 정의를 위해서는 관리자 접근을 위한 사용자 계정을 설정할 때, 강력한 비밀번호 정책을 적용하고, 불필요한 사용자 계정은 삭제해야 합니다. 또한, 관리자 페이지에 대한 접근은 IP 화이트리스트를 통해 제한하는 것이 좋습니다. 
+[시크릿 관리]: tomcat-users.xml 파일에 하드코딩된 사용자 정보는 환경 변수(.env)로 분리하여 관리해야 하며, 이 파일은 서버의 접근이 제한된 위치에 두어야 합니다.</t>
         </is>
       </c>
     </row>
@@ -518,7 +520,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-18 10:58:11</t>
+          <t>2026-05-19 02:02:20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -528,17 +530,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CWE-20</t>
+          <t>CWE-79</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>A01:2021-Broken Access Control</t>
+          <t>A03:2021-Injection</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>리디렉션 취약점</t>
+          <t>XSS(교차 사이트 스크립팅) 취약점</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -548,12 +550,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>메타 태그를 사용하여 2초 후에 특정 URL로 리디렉션하고 있습니다. 이 URL이 외부 도메인으로 설정되어 있어, 사용자가 의도하지 않은 사이트로 리디렉션될 수 있는 위험이 존재합니다.</t>
+          <t>HTML 소스코드에서 사용자 입력을 처리하는 부분이 보이지 않지만, 외부 링크를 포함한 여러 요소가 존재합니다. 만약 이러한 링크가 사용자 입력을 통해 동적으로 생성된다면, XSS 공격에 취약할 수 있습니다.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>리디렉션을 수행하는 메타 태그를 제거하고, 서버 측에서 리디렉션을 처리하도록 수정해야 합니다. 또한, 리디렉션할 URL을 검증하여 신뢰할 수 있는 도메인으로만 리디렉션되도록 해야 합니다. 하드코딩된 URL이 있다면 이를 환경 변수로 관리하여 보안을 강화하는 것이 필요합니다.</t>
+          <t>[수정 위치]: 외부 링크를 포함한 모든 사용자 입력 처리 부분에서 검증을 강화해야 합니다. 
+[코드 레벨 가이드]: 사용자 입력을 처리할 때는 항상 입력값 검증을 수행하고, 출력 시에는 HTML 인코딩을 적용하여 스크립트가 실행되지 않도록 해야 합니다. 또한, Content Security Policy(CSP)를 설정하여 외부 스크립트의 실행을 제한하는 것이 좋습니다. 
+[시크릿 관리]: 외부 링크가 API 호출을 포함하는 경우, API 키와 같은 민감한 정보는 하드코딩하지 말고 환경 변수로 관리해야 하며, 이를 통해 보안을 강화해야 합니다.</t>
         </is>
       </c>
     </row>
